--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/Panel 7/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.60857</v>
+        <v>17.29186</v>
       </c>
       <c r="D2" t="n">
-        <v>17.49591</v>
+        <v>17.10559</v>
       </c>
       <c r="E2" t="n">
-        <v>17.85873</v>
+        <v>17.17963</v>
       </c>
       <c r="F2" t="n">
-        <v>44.69225</v>
+        <v>43.68261</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05353</v>
+        <v>0.05359</v>
       </c>
       <c r="H2" t="n">
-        <v>1.90314</v>
+        <v>1.89483</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.30139</v>
+        <v>17.80567</v>
       </c>
       <c r="D3" t="n">
-        <v>17.58917</v>
+        <v>17.27148</v>
       </c>
       <c r="E3" t="n">
-        <v>17.68472</v>
+        <v>17.44947</v>
       </c>
       <c r="F3" t="n">
-        <v>44.03667</v>
+        <v>43.44807</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05329</v>
+        <v>0.05275</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85448</v>
+        <v>1.94138</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.42804</v>
+        <v>17.95419</v>
       </c>
       <c r="D4" t="n">
-        <v>17.68001</v>
+        <v>17.36081</v>
       </c>
       <c r="E4" t="n">
-        <v>17.39194</v>
+        <v>17.77262</v>
       </c>
       <c r="F4" t="n">
-        <v>45.00632</v>
+        <v>44.52015</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05238</v>
+        <v>0.05222</v>
       </c>
       <c r="H4" t="n">
-        <v>1.91601</v>
+        <v>1.89364</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.5304</v>
+        <v>17.6695</v>
       </c>
       <c r="D6" t="n">
-        <v>16.81953</v>
+        <v>16.74733</v>
       </c>
       <c r="E6" t="n">
-        <v>16.99232</v>
+        <v>16.92014</v>
       </c>
       <c r="F6" t="n">
-        <v>22.33604</v>
+        <v>23.05944</v>
       </c>
       <c r="G6" t="n">
-        <v>35.712</v>
+        <v>35.60847</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.41963</v>
+        <v>17.40266</v>
       </c>
       <c r="D7" t="n">
-        <v>16.7834</v>
+        <v>16.27978</v>
       </c>
       <c r="E7" t="n">
-        <v>17.47433</v>
+        <v>16.87513</v>
       </c>
       <c r="F7" t="n">
-        <v>22.79633</v>
+        <v>22.3187</v>
       </c>
       <c r="G7" t="n">
-        <v>36.46127</v>
+        <v>35.39272</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.6318</v>
+        <v>17.40463</v>
       </c>
       <c r="D8" t="n">
-        <v>16.72004</v>
+        <v>16.45062</v>
       </c>
       <c r="E8" t="n">
-        <v>17.25432</v>
+        <v>16.97791</v>
       </c>
       <c r="F8" t="n">
-        <v>22.9061</v>
+        <v>22.12919</v>
       </c>
       <c r="G8" t="n">
-        <v>35.80536</v>
+        <v>35.68094</v>
       </c>
     </row>
   </sheetData>
